--- a/public/excel/sub_products_example.xlsx
+++ b/public/excel/sub_products_example.xlsx
@@ -24,45 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t xml:space="preserve">بارکد </t>
   </si>
   <si>
-    <t>سری ساخت - سال</t>
-  </si>
-  <si>
-    <t>سری ساخت - ماه</t>
-  </si>
-  <si>
-    <t>انبار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">برچسب </t>
-  </si>
-  <si>
-    <t>تاریخ تولید</t>
-  </si>
-  <si>
-    <t>تاریخ انقضا</t>
-  </si>
-  <si>
-    <t>محصول (ID یا نام)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ضعیت (غیرفعال، فعال،مرجوعی) </t>
-  </si>
-  <si>
-    <t>تستی</t>
-  </si>
-  <si>
-    <t>فعال</t>
-  </si>
-  <si>
-    <t>انبار اصلی</t>
-  </si>
-  <si>
-    <t>لپتاپ</t>
+    <t>محصول (ID)</t>
   </si>
 </sst>
 </file>
@@ -117,7 +84,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -126,9 +93,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -412,77 +376,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="26.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41.109375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="B2" s="3">
         <v>215454545</v>
-      </c>
-      <c r="C2" s="3">
-        <v>139347</v>
-      </c>
-      <c r="D2" s="3">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="4">
-        <v>44958</v>
-      </c>
-      <c r="G2" s="4">
-        <v>47123</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
